--- a/site/exports/hit-shenzhen-computer.xlsx
+++ b/site/exports/hit-shenzhen-computer.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0b4ec8a49a014d8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R38c2ca25e7584f68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rd9048d5375e24593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rd524e3a70f6242fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R744f1acab08f4b79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8bc4a9bdae644667"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R5dbf1f129a274ae8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rc892d932de8d4e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R1e8e5b73d0b04f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rf475ceb738df43a0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -17,6 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
@@ -58,13 +61,21 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="10">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -128,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T1_0" displayName="T1_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -143,7 +154,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T1_1" displayName="T1_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T2_1" displayName="T2_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -168,7 +179,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T1_2" displayName="T1_2" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T2_2" displayName="T2_2" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
@@ -186,7 +197,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T1_3" displayName="T1_3" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T2_3" displayName="T2_3" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -204,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T1_4" displayName="T1_4" ref="A1:E4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T2_4" displayName="T2_4" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -421,55 +432,55 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>校区</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>院系</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>官方主页</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>核对日期</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>缺项与冲突</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>范围</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>深圳</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>信息学部/计算机科学与技术学院</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
-        <x:v>2026-10-23</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="E2" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
         <x:v>样本记录，不代表该院系全体教师；只收录已核实公开信息。；未找到硕士学位证据，不能填为无硕士。；博士入学月份中英文履历冲突。；英文工作经历旧版仍称副教授，中文正文2022.01起教授；采用较新中文记录并保留冲突。</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb6cea1b8021844f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R915206aac66f4914"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -498,187 +509,187 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>事件类型</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>阶段/职位</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>机构</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>开始</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>结束</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>专业</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>国家</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>地区</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>洲</x:v>
       </x:c>
-      <x:c r="K1" s="5" t="str">
+      <x:c r="K1" s="9" t="str">
         <x:v>历史985分类</x:v>
       </x:c>
-      <x:c r="L1" s="5" t="str">
+      <x:c r="L1" s="9" t="str">
         <x:v>确证授位</x:v>
       </x:c>
-      <x:c r="M1" s="5" t="str">
+      <x:c r="M1" s="9" t="str">
         <x:v>授位日期</x:v>
       </x:c>
-      <x:c r="N1" s="5" t="str">
+      <x:c r="N1" s="9" t="str">
         <x:v>授位来源</x:v>
       </x:c>
-      <x:c r="O1" s="5" t="str">
+      <x:c r="O1" s="9" t="str">
         <x:v>备注及冲突</x:v>
       </x:c>
-      <x:c r="P1" s="5" t="str">
+      <x:c r="P1" s="9" t="str">
         <x:v>地域口径</x:v>
       </x:c>
-      <x:c r="Q1" s="5" t="str">
+      <x:c r="Q1" s="9" t="str">
         <x:v>来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>degree</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>学士</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>华中师范大学</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="6" t="str">
         <x:v>1999-09</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>2003-06</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>计算机科学与技术</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>中国</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="I2" s="6" t="str">
         <x:v>中国内地</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="6" t="str">
         <x:v>亚洲</x:v>
       </x:c>
-      <x:c r="K2" s="3" t="str">
+      <x:c r="K2" s="6" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="L2" s="9" t="b">
+      <x:c r="L2" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M2" s="3" t="str"/>
-      <x:c r="N2" s="3" t="str"/>
-      <x:c r="O2" s="3" t="str"/>
-      <x:c r="P2" s="3" t="str">
+      <x:c r="M2" s="7" t="str"/>
+      <x:c r="N2" s="6" t="str"/>
+      <x:c r="O2" s="6" t="str"/>
+      <x:c r="P2" s="6" t="str">
         <x:v>院校所在地标准化，不代表个人国籍或全部实际学习地点；中国香港单列，不归为国外。</x:v>
       </x:c>
-      <x:c r="Q2" s="3" t="str">
+      <x:c r="Q2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="B3" s="6" t="str">
         <x:v>degree</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>香港城市大学</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
+      <x:c r="E3" s="6" t="str">
         <x:v>2004</x:v>
       </x:c>
-      <x:c r="F3" s="3" t="str">
+      <x:c r="F3" s="6" t="str">
         <x:v>2008-09</x:v>
       </x:c>
-      <x:c r="G3" s="3" t="str">
+      <x:c r="G3" s="6" t="str">
         <x:v>计算机科学</x:v>
       </x:c>
-      <x:c r="H3" s="3" t="str">
+      <x:c r="H3" s="6" t="str">
         <x:v>中国</x:v>
       </x:c>
-      <x:c r="I3" s="3" t="str">
+      <x:c r="I3" s="6" t="str">
         <x:v>中国香港</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="str">
+      <x:c r="J3" s="6" t="str">
         <x:v>亚洲</x:v>
       </x:c>
-      <x:c r="K3" s="3" t="str">
+      <x:c r="K3" s="6" t="str">
         <x:v>no</x:v>
       </x:c>
-      <x:c r="L3" s="9" t="b">
+      <x:c r="L3" s="13" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="M3" s="3" t="str"/>
-      <x:c r="N3" s="3" t="str"/>
-      <x:c r="O3" s="3" t="str">
+      <x:c r="M3" s="7" t="str"/>
+      <x:c r="N3" s="6" t="str"/>
+      <x:c r="O3" s="6" t="str">
         <x:v>中文履历入学2004.09，英文2004.08存在月份冲突；毕业履历2008.09，机构论文库授位2008-10-02，可能是不同事件，不混合。</x:v>
       </x:c>
-      <x:c r="P3" s="3" t="str">
+      <x:c r="P3" s="6" t="str">
         <x:v>院校所在地标准化，不代表个人国籍或全部实际学习地点；中国香港单列，不归为国外。</x:v>
       </x:c>
-      <x:c r="Q3" s="3" t="str">
+      <x:c r="Q3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="6" t="str">
         <x:v>employment</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>教授、博士生导师</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>哈尔滨工业大学</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str"/>
-      <x:c r="F4" s="3" t="str"/>
-      <x:c r="G4" s="3" t="str"/>
-      <x:c r="H4" s="3" t="str"/>
-      <x:c r="I4" s="3" t="str"/>
-      <x:c r="J4" s="3" t="str"/>
-      <x:c r="K4" s="3" t="str"/>
-      <x:c r="L4" s="3" t="str"/>
-      <x:c r="M4" s="3" t="str"/>
-      <x:c r="N4" s="3" t="str"/>
-      <x:c r="O4" s="3" t="str"/>
-      <x:c r="P4" s="3" t="str"/>
-      <x:c r="Q4" s="3" t="str">
+      <x:c r="E4" s="6" t="str"/>
+      <x:c r="F4" s="6" t="str"/>
+      <x:c r="G4" s="6" t="str"/>
+      <x:c r="H4" s="6" t="str"/>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str"/>
+      <x:c r="K4" s="6" t="str"/>
+      <x:c r="L4" s="6" t="str"/>
+      <x:c r="M4" s="7" t="str"/>
+      <x:c r="N4" s="6" t="str"/>
+      <x:c r="O4" s="6" t="str"/>
+      <x:c r="P4" s="6" t="str"/>
+      <x:c r="Q4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fd8c7c833d34dc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc2d8610bdd48d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -700,73 +711,73 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>导师姓名</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>关系类型</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>阶段</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>简介</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>在职状态</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>状态说明</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>已核在职主页</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>关系来源</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>任职来源</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>Xiaohua Jia</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>博士导师</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>博士</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="E2" s="6" t="str">
         <x:v>香港城市大学计算机系讲座教授，研究分布式系统、网络、云计算及数据安全。</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>active_officially_listed</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>官方主页列1996-present CityU任职，查阅日2026-10-23。</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>https://www.cs.cityu.edu.hk/~jia/</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str">
+      <x:c r="I2" s="6" t="str">
         <x:v>https://scholars.cityu.edu.hk/en/studentTheses/virtual-backbone-construction-and-energy-efficient-routing-in-wir/</x:v>
       </x:c>
-      <x:c r="J2" s="3" t="str">
+      <x:c r="J2" s="6" t="str">
         <x:v>https://www.cs.cityu.edu.hk/~jia/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra375e304d3184bd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cbb424915f04f9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -788,67 +799,67 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>标题</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>年份</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>DOI</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>链接</x:v>
       </x:c>
-      <x:c r="F1" s="5" t="str">
+      <x:c r="F1" s="9" t="str">
         <x:v>类型</x:v>
       </x:c>
-      <x:c r="G1" s="5" t="str">
+      <x:c r="G1" s="9" t="str">
         <x:v>收录来源</x:v>
       </x:c>
-      <x:c r="H1" s="5" t="str">
+      <x:c r="H1" s="9" t="str">
         <x:v>作者归属依据</x:v>
       </x:c>
-      <x:c r="I1" s="5" t="str">
+      <x:c r="I1" s="9" t="str">
         <x:v>链接核验范围</x:v>
       </x:c>
-      <x:c r="J1" s="5" t="str">
+      <x:c r="J1" s="9" t="str">
         <x:v>备注</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>Virtual backbone construction and energy efficient routing in wireless ad hoc and sensor networks</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="n">
+      <x:c r="C2" s="6" t="n">
         <x:v>2008</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str"/>
-      <x:c r="E2" s="3" t="str">
+      <x:c r="D2" s="6" t="str"/>
+      <x:c r="E2" s="6" t="str">
         <x:v>https://scholars.cityu.edu.hk/en/studentTheses/virtual-backbone-construction-and-energy-efficient-routing-in-wir/</x:v>
       </x:c>
-      <x:c r="F2" s="3" t="str">
+      <x:c r="F2" s="6" t="str">
         <x:v>doctoral_thesis</x:v>
       </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="G2" s="6" t="str">
         <x:v>https://scholars.cityu.edu.hk/en/studentTheses/virtual-backbone-construction-and-energy-efficient-routing-in-wir/</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="str">
+      <x:c r="H2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
-      <x:c r="I2" s="3" t="str"/>
-      <x:c r="J2" s="3" t="str"/>
+      <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc7e538471b445b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4c96a281e884a07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -865,77 +876,94 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="5" t="str">
+      <x:c r="A1" s="9" t="str">
         <x:v>姓名</x:v>
       </x:c>
-      <x:c r="B1" s="5" t="str">
+      <x:c r="B1" s="9" t="str">
         <x:v>来源ID</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="str">
+      <x:c r="C1" s="9" t="str">
         <x:v>链接</x:v>
       </x:c>
-      <x:c r="D1" s="5" t="str">
+      <x:c r="D1" s="9" t="str">
         <x:v>核验方式</x:v>
       </x:c>
-      <x:c r="E1" s="5" t="str">
+      <x:c r="E1" s="9" t="str">
         <x:v>查阅日期</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
-      <x:c r="A2" s="3" t="str">
+      <x:c r="A2" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B2" s="3" t="str">
+      <x:c r="B2" s="6" t="str">
         <x:v>duhongwei-official</x:v>
       </x:c>
-      <x:c r="C2" s="3" t="str">
+      <x:c r="C2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
-      <x:c r="D2" s="3" t="str">
+      <x:c r="D2" s="6" t="str">
         <x:v>official_page_public_body_fetched</x:v>
       </x:c>
-      <x:c r="E2" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E2" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
-      <x:c r="A3" s="3" t="str">
+      <x:c r="A3" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B3" s="3" t="str">
+      <x:c r="B3" s="6" t="str">
         <x:v>jia-profile</x:v>
       </x:c>
-      <x:c r="C3" s="3" t="str">
+      <x:c r="C3" s="6" t="str">
         <x:v>https://www.cs.cityu.edu.hk/~jia/</x:v>
       </x:c>
-      <x:c r="D3" s="3" t="str">
+      <x:c r="D3" s="6" t="str">
         <x:v>official_profile_read</x:v>
       </x:c>
-      <x:c r="E3" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E3" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
-      <x:c r="A4" s="3" t="str">
+      <x:c r="A4" s="6" t="str">
         <x:v>堵宏伟</x:v>
       </x:c>
-      <x:c r="B4" s="3" t="str">
+      <x:c r="B4" s="6" t="str">
         <x:v>hit-duhongwei-publication-1</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="str">
+      <x:c r="C4" s="6" t="str">
         <x:v>https://scholars.cityu.edu.hk/en/studentTheses/virtual-backbone-construction-and-energy-efficient-routing-in-wir/</x:v>
       </x:c>
-      <x:c r="D4" s="3" t="str">
+      <x:c r="D4" s="6" t="str">
         <x:v>official_publisher_or_institution_metadata</x:v>
       </x:c>
-      <x:c r="E4" s="3" t="str">
-        <x:v>2026-10-23</x:v>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="64" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>堵宏伟</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E5" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19260e7b9efb424a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R903c840a3ce249c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-computer.xlsx
+++ b/site/exports/hit-shenzhen-computer.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8bc4a9bdae644667"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R5dbf1f129a274ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rc892d932de8d4e78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R1e8e5b73d0b04f6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="Rf475ceb738df43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9c7198360f7b467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R2f0012633e694d51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R8f30206e9b8246eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8642827c6ccf402a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R70195c1643134066"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:G2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="7">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:I2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="9">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -148,6 +148,8 @@
     <x:tableColumn id="5" name="核对日期"/>
     <x:tableColumn id="6" name="缺项与冲突"/>
     <x:tableColumn id="7" name="范围"/>
+    <x:tableColumn id="8" name="主页可用性"/>
+    <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -429,6 +431,8 @@
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -453,6 +457,12 @@
       <x:c r="G1" s="9" t="str">
         <x:v>范围</x:v>
       </x:c>
+      <x:c r="H1" s="9" t="str">
+        <x:v>主页可用性</x:v>
+      </x:c>
+      <x:c r="I1" s="9" t="str">
+        <x:v>替代官方职业报道（非个人主页）</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -476,11 +486,15 @@
       <x:c r="G2" s="6" t="str">
         <x:v>分批核实资料，不是完整名录</x:v>
       </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R915206aac66f4914"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ade4055e7e64947"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -689,7 +703,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dc2d8610bdd48d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddfef9a0eb79477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -777,7 +791,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cbb424915f04f9f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R648fa39ab37a479e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -859,7 +873,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4c96a281e884a07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ead68244c8b431d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -963,7 +977,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R903c840a3ce249c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f362e3d937d4ade"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-computer.xlsx
+++ b/site/exports/hit-shenzhen-computer.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9c7198360f7b467d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R2f0012633e694d51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="R8f30206e9b8246eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R8642827c6ccf402a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R70195c1643134066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R557fc0a586484d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="R40851399acfb40ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rc5797ced653c49bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="R412e4505aa3c4d58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R3417667e3ada4ce1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,8 +139,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:I2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="9">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2_0" displayName="T2_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
     <x:tableColumn id="3" name="院系"/>
@@ -150,14 +150,16 @@
     <x:tableColumn id="7" name="范围"/>
     <x:tableColumn id="8" name="主页可用性"/>
     <x:tableColumn id="9" name="替代官方职业报道（非个人主页）"/>
+    <x:tableColumn id="10" name="所属学校ID"/>
+    <x:tableColumn id="11" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T2_1" displayName="T2_1" ref="A1:Q4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="17">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T2_1" displayName="T2_1" ref="A1:S4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
     <x:tableColumn id="3" name="阶段/职位"/>
@@ -175,14 +177,16 @@
     <x:tableColumn id="15" name="备注及冲突"/>
     <x:tableColumn id="16" name="地域口径"/>
     <x:tableColumn id="17" name="来源"/>
+    <x:tableColumn id="18" name="所属学校ID"/>
+    <x:tableColumn id="19" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T2_2" displayName="T2_2" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T2_2" displayName="T2_2" ref="A1:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="导师姓名"/>
     <x:tableColumn id="3" name="关系类型"/>
@@ -193,14 +197,16 @@
     <x:tableColumn id="8" name="已核在职主页"/>
     <x:tableColumn id="9" name="关系来源"/>
     <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T2_3" displayName="T2_3" ref="A1:J2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T2_3" displayName="T2_3" ref="A1:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
     <x:tableColumn id="3" name="年份"/>
@@ -211,19 +217,23 @@
     <x:tableColumn id="8" name="作者归属依据"/>
     <x:tableColumn id="9" name="链接核验范围"/>
     <x:tableColumn id="10" name="备注"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T2_4" displayName="T2_4" ref="A1:E5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="5">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T2_4" displayName="T2_4" ref="A1:G5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
     <x:tableColumn id="3" name="链接"/>
     <x:tableColumn id="4" name="核验方式"/>
     <x:tableColumn id="5" name="查阅日期"/>
+    <x:tableColumn id="6" name="所属学校ID"/>
+    <x:tableColumn id="7" name="所属学校"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -433,6 +443,8 @@
     <x:col min="7" max="7" width="55" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="26" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="26" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -463,6 +475,12 @@
       <x:c r="I1" s="9" t="str">
         <x:v>替代官方职业报道（非个人主页）</x:v>
       </x:c>
+      <x:c r="J1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -490,11 +508,17 @@
         <x:v>公开个人页（时效以核对日为准）</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str"/>
+      <x:c r="J2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ade4055e7e64947"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82851f5e2e25414c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -520,6 +544,8 @@
     <x:col min="15" max="15" width="55" hidden="0" customWidth="1"/>
     <x:col min="16" max="16" width="26" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="55" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="26" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -574,6 +600,12 @@
       <x:c r="Q1" s="9" t="str">
         <x:v>来源</x:v>
       </x:c>
+      <x:c r="R1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="S1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -621,6 +653,12 @@
       <x:c r="Q2" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
+      <x:c r="R2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -669,6 +707,12 @@
       </x:c>
       <x:c r="Q3" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
+      </x:c>
+      <x:c r="R3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
@@ -699,11 +743,17 @@
       <x:c r="Q4" s="6" t="str">
         <x:v>https://homepage.hit.edu.cn/duhongwei</x:v>
       </x:c>
+      <x:c r="R4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="S4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddfef9a0eb79477e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R431dd8f21a0f46ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -722,6 +772,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -755,6 +807,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>任职来源</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -787,11 +845,17 @@
       <x:c r="J2" s="6" t="str">
         <x:v>https://www.cs.cityu.edu.hk/~jia/</x:v>
       </x:c>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R648fa39ab37a479e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5dbe7de3a0c04c17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -810,6 +874,8 @@
     <x:col min="8" max="8" width="26" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="55" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="55" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="26" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -843,6 +909,12 @@
       <x:c r="J1" s="9" t="str">
         <x:v>备注</x:v>
       </x:c>
+      <x:c r="K1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="L1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -869,11 +941,17 @@
       </x:c>
       <x:c r="I2" s="6" t="str"/>
       <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ead68244c8b431d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69166e31b8dc49fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -887,6 +965,8 @@
     <x:col min="3" max="3" width="55" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -905,6 +985,12 @@
       <x:c r="E1" s="9" t="str">
         <x:v>查阅日期</x:v>
       </x:c>
+      <x:c r="F1" s="9" t="str">
+        <x:v>所属学校ID</x:v>
+      </x:c>
+      <x:c r="G1" s="9" t="str">
+        <x:v>所属学校</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="64" customHeight="1">
       <x:c r="A2" s="6" t="str">
@@ -922,6 +1008,12 @@
       <x:c r="E2" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="64" customHeight="1">
       <x:c r="A3" s="6" t="str">
@@ -939,6 +1031,12 @@
       <x:c r="E3" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="64" customHeight="1">
       <x:c r="A4" s="6" t="str">
@@ -956,6 +1054,12 @@
       <x:c r="E4" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
@@ -973,11 +1077,17 @@
       <x:c r="E5" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
       </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>hit</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>哈尔滨工业大学</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f362e3d937d4ade"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb16ea3657b44948"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/hit-shenzhen-computer.xlsx
+++ b/site/exports/hit-shenzhen-computer.xlsx
@@ -452,8 +452,8 @@
     <col width="51.8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
